--- a/test_samples/MAERSK/sample2_ref.xlsx
+++ b/test_samples/MAERSK/sample2_ref.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="24375" yWindow="-11070" windowWidth="15225" windowHeight="8235" tabRatio="819" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="22290" yWindow="-10890" windowWidth="15225" windowHeight="8235" tabRatio="819" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="DWIHARTA" sheetId="1" state="visible" r:id="rId1"/>
@@ -656,7 +656,7 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0902978980</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
@@ -670,8 +670,10 @@
           <t>JKT3328339</t>
         </is>
       </c>
-      <c r="L2" s="0" t="n">
-        <v>5617858220</v>
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M2" s="0" t="inlineStr">
         <is>
@@ -734,7 +736,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0902978980</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
@@ -748,8 +750,10 @@
           <t>JKT3328339</t>
         </is>
       </c>
-      <c r="L3" s="0" t="n">
-        <v>5617858220</v>
+      <c r="L3" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M3" s="0" t="inlineStr">
         <is>
@@ -812,7 +816,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0902978980</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
@@ -826,8 +830,10 @@
           <t>JKT3328339</t>
         </is>
       </c>
-      <c r="L4" s="0" t="n">
-        <v>5617858220</v>
+      <c r="L4" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M4" s="0" t="inlineStr">
         <is>
@@ -890,7 +896,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0902978980</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
@@ -904,8 +910,10 @@
           <t>JKT3328339</t>
         </is>
       </c>
-      <c r="L5" s="0" t="n">
-        <v>5617858220</v>
+      <c r="L5" s="0" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M5" s="0" t="inlineStr">
         <is>
